--- a/ascend_test_suite/2.2.RC1-800I-A2-py311-openeuler24.03-lts/model_list.xlsx
+++ b/ascend_test_suite/2.2.RC1-800I-A2-py311-openeuler24.03-lts/model_list.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zhang\Documents\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5A582C1-9BEF-45CC-90DA-19E8B2D040DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="17230"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MindIE" sheetId="1" r:id="rId1"/>
@@ -18,8 +24,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -27,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="90">
   <si>
     <t>模型名称</t>
   </si>
@@ -420,50 +424,56 @@
     <t>chatglm2-6b</t>
   </si>
   <si>
-    <t>910B2</t>
-  </si>
-  <si>
     <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5 --model chatglm2-6b --tokenizer /home/weight/chatglm2-6b -tp 1 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 2048 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40</t>
   </si>
   <si>
     <t>chatglm3-6b</t>
   </si>
   <si>
-    <t>910B3</t>
-  </si>
-  <si>
     <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5 --model chatglm3-6b --tokenizer /home/weight/chatglm3-6b -tp 1 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 2048 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40</t>
   </si>
   <si>
     <t>baichuan-7B</t>
   </si>
   <si>
-    <t>910B4</t>
-  </si>
-  <si>
     <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5 --model baichuan-7B --tokenizer /home/weight/baichuan-7B -tp 1 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 2048 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40</t>
   </si>
   <si>
     <t>Baichuan2-7B-Chat</t>
   </si>
   <si>
-    <t>910B5</t>
-  </si>
-  <si>
     <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5 --model Baichuan2-7B-Chat --tokenizer /home/weight/Baichuan2-7B-Chat -tp 1 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 2048 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40</t>
+  </si>
+  <si>
+    <t>Qwen3.5-27B</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Qwen3.5-35B-A3B</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5 --model Qwen3.5-35B-A3B --tokenizer /home/weight/Qwen3.5-35B-A3B -tp 1 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 2048 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40 --tool-call-parser hermes</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5 --model Qwen3.5-27B --tokenizer /home/weight/Qwen3.5-27B -tp 2 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 2048 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40 --tool-call-parser hermes</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Qwen3-32B-FP8</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5 --model Qwen3-32B-FP8 --tokenizer /home/weight/Qwen3/Qwen3-32B-FP8 -tp 2 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 2048 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40 --tool-call-parser hermes</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="23">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -493,345 +503,29 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -856,253 +550,22 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FFDEE0E3"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FFDEE0E3"/>
       </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1115,90 +578,165 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
       <border>
@@ -1209,7 +747,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="0"/>
       </font>
       <fill>
@@ -1237,154 +775,40 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.39994506668294322"/>
         </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="16"/>
+      <tableStyleElement type="headerRow" dxfId="15"/>
+      <tableStyleElement type="totalRow" dxfId="14"/>
+      <tableStyleElement type="firstColumn" dxfId="13"/>
+      <tableStyleElement type="lastColumn" dxfId="12"/>
+      <tableStyleElement type="firstRowStripe" dxfId="11"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="9"/>
+      <tableStyleElement type="totalRow" dxfId="8"/>
+      <tableStyleElement type="firstRowStripe" dxfId="7"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
+      <tableStyleElement type="pageFieldValues" dxfId="0"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1634,22 +1058,22 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:T40"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:T43"/>
+  <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="39.9090909090909" customWidth="1"/>
-    <col min="2" max="2" width="6.54545454545455" customWidth="1"/>
-    <col min="3" max="3" width="255.636363636364" customWidth="1"/>
-    <col min="4" max="4" width="51.6363636363636" customWidth="1"/>
+    <col min="1" max="1" width="29.1328125" customWidth="1"/>
+    <col min="2" max="2" width="6.53125" customWidth="1"/>
+    <col min="3" max="3" width="255.59765625" customWidth="1"/>
+    <col min="4" max="4" width="51.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1679,7 +1103,7 @@
       <c r="S1" s="2"/>
       <c r="T1" s="2"/>
     </row>
-    <row r="2" spans="1:20">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1709,7 +1133,7 @@
       <c r="S2" s="2"/>
       <c r="T2" s="2"/>
     </row>
-    <row r="3" spans="1:20">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -1737,7 +1161,7 @@
       <c r="S3" s="2"/>
       <c r="T3" s="2"/>
     </row>
-    <row r="4" spans="1:20">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -1765,7 +1189,7 @@
       <c r="S4" s="2"/>
       <c r="T4" s="2"/>
     </row>
-    <row r="5" spans="1:20">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
@@ -1795,7 +1219,7 @@
       <c r="S5" s="2"/>
       <c r="T5" s="2"/>
     </row>
-    <row r="6" spans="1:20">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -1825,7 +1249,7 @@
       <c r="S6" s="2"/>
       <c r="T6" s="2"/>
     </row>
-    <row r="7" spans="1:20">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
@@ -1853,7 +1277,7 @@
       <c r="S7" s="2"/>
       <c r="T7" s="2"/>
     </row>
-    <row r="8" spans="1:20">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>18</v>
       </c>
@@ -1881,7 +1305,7 @@
       <c r="S8" s="2"/>
       <c r="T8" s="2"/>
     </row>
-    <row r="9" spans="1:20">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>20</v>
       </c>
@@ -1909,7 +1333,7 @@
       <c r="S9" s="2"/>
       <c r="T9" s="2"/>
     </row>
-    <row r="10" spans="1:20">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>22</v>
       </c>
@@ -1937,7 +1361,7 @@
       <c r="S10" s="2"/>
       <c r="T10" s="2"/>
     </row>
-    <row r="11" spans="1:20">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>24</v>
       </c>
@@ -1965,7 +1389,7 @@
       <c r="S11" s="2"/>
       <c r="T11" s="2"/>
     </row>
-    <row r="12" spans="1:20">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>26</v>
       </c>
@@ -1993,7 +1417,7 @@
       <c r="S12" s="2"/>
       <c r="T12" s="2"/>
     </row>
-    <row r="13" spans="1:20">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>28</v>
       </c>
@@ -2021,7 +1445,7 @@
       <c r="S13" s="2"/>
       <c r="T13" s="2"/>
     </row>
-    <row r="14" spans="1:20">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>30</v>
       </c>
@@ -2049,7 +1473,7 @@
       <c r="S14" s="2"/>
       <c r="T14" s="2"/>
     </row>
-    <row r="15" spans="1:20">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>32</v>
       </c>
@@ -2077,7 +1501,7 @@
       <c r="S15" s="2"/>
       <c r="T15" s="2"/>
     </row>
-    <row r="16" spans="1:20">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>34</v>
       </c>
@@ -2105,7 +1529,7 @@
       <c r="S16" s="2"/>
       <c r="T16" s="2"/>
     </row>
-    <row r="17" spans="1:20">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>36</v>
       </c>
@@ -2133,7 +1557,7 @@
       <c r="S17" s="2"/>
       <c r="T17" s="2"/>
     </row>
-    <row r="18" spans="1:20">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>38</v>
       </c>
@@ -2161,7 +1585,7 @@
       <c r="S18" s="2"/>
       <c r="T18" s="2"/>
     </row>
-    <row r="19" spans="1:20">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>40</v>
       </c>
@@ -2189,7 +1613,7 @@
       <c r="S19" s="2"/>
       <c r="T19" s="2"/>
     </row>
-    <row r="20" spans="1:20">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>42</v>
       </c>
@@ -2217,7 +1641,7 @@
       <c r="S20" s="2"/>
       <c r="T20" s="2"/>
     </row>
-    <row r="21" spans="1:20">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>44</v>
       </c>
@@ -2245,7 +1669,7 @@
       <c r="S21" s="2"/>
       <c r="T21" s="2"/>
     </row>
-    <row r="22" spans="1:20">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>46</v>
       </c>
@@ -2273,7 +1697,7 @@
       <c r="S22" s="1"/>
       <c r="T22" s="1"/>
     </row>
-    <row r="23" spans="1:20">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>48</v>
       </c>
@@ -2301,7 +1725,7 @@
       <c r="S23" s="2"/>
       <c r="T23" s="2"/>
     </row>
-    <row r="24" spans="1:20">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>50</v>
       </c>
@@ -2329,7 +1753,7 @@
       <c r="S24" s="2"/>
       <c r="T24" s="2"/>
     </row>
-    <row r="25" spans="1:20">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>52</v>
       </c>
@@ -2357,7 +1781,7 @@
       <c r="S25" s="2"/>
       <c r="T25" s="2"/>
     </row>
-    <row r="26" spans="1:20">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>54</v>
       </c>
@@ -2385,7 +1809,7 @@
       <c r="S26" s="2"/>
       <c r="T26" s="2"/>
     </row>
-    <row r="27" spans="1:20">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>56</v>
       </c>
@@ -2413,7 +1837,7 @@
       <c r="S27" s="2"/>
       <c r="T27" s="2"/>
     </row>
-    <row r="28" spans="1:20">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>58</v>
       </c>
@@ -2441,7 +1865,7 @@
       <c r="S28" s="2"/>
       <c r="T28" s="2"/>
     </row>
-    <row r="29" spans="1:20">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>60</v>
       </c>
@@ -2469,7 +1893,7 @@
       <c r="S29" s="2"/>
       <c r="T29" s="2"/>
     </row>
-    <row r="30" spans="1:20">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>62</v>
       </c>
@@ -2497,7 +1921,7 @@
       <c r="S30" s="1"/>
       <c r="T30" s="1"/>
     </row>
-    <row r="31" spans="1:20">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>64</v>
       </c>
@@ -2525,7 +1949,7 @@
       <c r="S31" s="2"/>
       <c r="T31" s="2"/>
     </row>
-    <row r="32" spans="1:20">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>66</v>
       </c>
@@ -2553,7 +1977,7 @@
       <c r="S32" s="2"/>
       <c r="T32" s="2"/>
     </row>
-    <row r="33" spans="1:20">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>68</v>
       </c>
@@ -2581,7 +2005,7 @@
       <c r="S33" s="1"/>
       <c r="T33" s="1"/>
     </row>
-    <row r="34" spans="1:20">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>70</v>
       </c>
@@ -2609,7 +2033,7 @@
       <c r="S34" s="2"/>
       <c r="T34" s="2"/>
     </row>
-    <row r="35" spans="1:20">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>72</v>
       </c>
@@ -2637,7 +2061,7 @@
       <c r="S35" s="2"/>
       <c r="T35" s="2"/>
     </row>
-    <row r="36" spans="1:20">
+    <row r="36" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>74</v>
       </c>
@@ -2665,15 +2089,15 @@
       <c r="S36" s="2"/>
       <c r="T36" s="2"/>
     </row>
-    <row r="37" spans="1:20">
+    <row r="37" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>76</v>
       </c>
       <c r="B37" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C37" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>78</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
@@ -2693,15 +2117,15 @@
       <c r="S37" s="2"/>
       <c r="T37" s="2"/>
     </row>
-    <row r="38" spans="1:20">
+    <row r="38" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>79</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>81</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
@@ -2721,15 +2145,15 @@
       <c r="S38" s="2"/>
       <c r="T38" s="2"/>
     </row>
-    <row r="39" spans="1:20">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>83</v>
+        <v>5</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
@@ -2749,15 +2173,15 @@
       <c r="S39" s="2"/>
       <c r="T39" s="2"/>
     </row>
-    <row r="40" spans="1:20">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>86</v>
+        <v>5</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" s="2"/>
@@ -2777,11 +2201,44 @@
       <c r="S40" s="2"/>
       <c r="T40" s="2"/>
     </row>
+    <row r="41" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A41" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A42" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A43" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" display="docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e &quot;ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7&quot; docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5 --model DeepSeek-R1-AWQ --tokenizer /home/weight/DeepSeek-R1-AWQ/ -tp 8 --port 4321 --platform-type ascend --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --quantization awq --swap-space 40 --gpu-memory-utilization 0.9" tooltip="http://docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5"/>
+    <hyperlink ref="C2" r:id="rId1" tooltip="http://docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5" display="docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e &quot;ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7&quot; docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5 --model DeepSeek-R1-AWQ --tokenizer /home/weight/DeepSeek-R1-AWQ/ -tp 8 --port 4321 --platform-type ascend --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --quantization awq --swap-space 40 --gpu-memory-utilization 0.9" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>